--- a/data/argentina/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/argentina/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC17"/>
+  <dimension ref="A1:BC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,35 +707,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>noM4eJv9</t>
+          <t>fotMKZ7K</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45506.83333333334</v>
+        <v>45513.625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">espinoza f 
+          <t xml:space="preserve">mastrangelo h 
   arg </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio marcelo bielsa
-  rosario </t>
+          <t xml:space="preserve">estadio guillermo laza
+  buenos aires </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>42000</v>
+        <v>3000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6gMiRHVj</t>
+          <t>2iZ4q0z6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>p2SkCHXs</t>
+          <t>Y9yh1J7G</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -760,169 +760,143 @@
           <t>liga profesional</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>4QmJ2LNc</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>175</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>59</v>
-      </c>
-      <c r="U2" t="n">
-        <v>575000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>75</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>GIb40wNM</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="X2" t="n">
-        <v>176</v>
+        <v>179.3333333333333</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA2" t="n">
-        <v>69</v>
+        <v>414</v>
       </c>
       <c r="AB2" t="n">
-        <v>1900000</v>
+        <v>13275000</v>
       </c>
       <c r="AC2" t="n">
-        <v>72</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>27.16296296296296</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>178.0666666666667</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.107407407407407</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>70.9074074074074</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2480740.740740741</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>73.7037037037037</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>27.85185185185185</v>
+        <v>26.9790404040404</v>
       </c>
       <c r="AK2" t="n">
-        <v>175.7037037037037</v>
+        <v>177.5767676767677</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.148148148148148</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>71.55555555555556</v>
+        <v>70.4128787878788</v>
       </c>
       <c r="AN2" t="n">
-        <v>2891666.666666667</v>
+        <v>3041502.525252525</v>
       </c>
       <c r="AO2" t="n">
-        <v>73.8888888888889</v>
+        <v>73.53232323232324</v>
       </c>
       <c r="AP2" t="n">
-        <v>24.41805555555555</v>
+        <v>29.97333333333334</v>
       </c>
       <c r="AQ2" t="n">
-        <v>174.113425925926</v>
+        <v>177.88</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.072685185185185</v>
+        <v>1</v>
       </c>
       <c r="AS2" t="n">
-        <v>65.91157407407407</v>
+        <v>66.52000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>1480254.62962963</v>
+        <v>695000</v>
       </c>
       <c r="AU2" t="n">
-        <v>71.95601851851852</v>
+        <v>67.25333333333333</v>
       </c>
       <c r="AV2" t="n">
-        <v>28.24166666666667</v>
+        <v>26.95279520020568</v>
       </c>
       <c r="AW2" t="n">
-        <v>177.9375</v>
+        <v>178.4702570400141</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.225</v>
+        <v>1</v>
       </c>
       <c r="AY2" t="n">
-        <v>68.98333333333333</v>
+        <v>70.04219407569791</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1364895.833333333</v>
+        <v>2381886.146970866</v>
       </c>
       <c r="BA2" t="n">
-        <v>72.675</v>
+        <v>73.46317034060002</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>xvR2CVDc</t>
+          <t>YgyxEvnR</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>xYveDhra</t>
+          <t>nozaSkhA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nkx6zI2q</t>
+          <t>YHCv8dOE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45507.625</v>
+        <v>45513.6875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">gariano a 
+          <t xml:space="preserve">trucco s 
   arg </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio malvinas argentinas
-  mendoza </t>
+          <t xml:space="preserve">claudio fabian tapia
+  barracas </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>42000</v>
+        <v>4400</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>tUAxIm6l</t>
+          <t>hW08cP6J</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>QuxS0ahA</t>
+          <t>bkDdeAvA</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -947,153 +921,159 @@
           <t>liga profesional</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>xd3lGq3F</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Amzaty2s</t>
+        </is>
+      </c>
       <c r="P3" t="n">
-        <v>23.66666666666667</v>
+        <v>22</v>
       </c>
       <c r="Q3" t="n">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>206</v>
+        <v>63</v>
       </c>
       <c r="U3" t="n">
-        <v>6100000</v>
+        <v>1000000</v>
       </c>
       <c r="V3" t="n">
-        <v>220</v>
-      </c>
-      <c r="W3" t="n">
-        <v>29</v>
-      </c>
-      <c r="X3" t="n">
-        <v>169</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>68</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>68</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>24.80793650793651</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>179.1198412698413</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>66.73730158730159</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1425158.73015873</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>71.39126984126985</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>24</v>
+        <v>25.9966588966589</v>
       </c>
       <c r="AK3" t="n">
-        <v>178.925925925926</v>
+        <v>180.4968919968919</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>69.1111111111111</v>
+        <v>70.41616161616162</v>
       </c>
       <c r="AN3" t="n">
-        <v>2338888.888888889</v>
+        <v>2743960.761460762</v>
       </c>
       <c r="AO3" t="n">
-        <v>74.81481481481482</v>
+        <v>74.18523698523698</v>
       </c>
       <c r="AP3" t="n">
-        <v>22.60622710622711</v>
+        <v>24.11363423761593</v>
       </c>
       <c r="AQ3" t="n">
-        <v>181.565934065934</v>
+        <v>176.8796477892817</v>
       </c>
       <c r="AR3" t="n">
         <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>68.45604395604396</v>
+        <v>65.95640679686447</v>
       </c>
       <c r="AT3" t="n">
-        <v>2499557.387057387</v>
+        <v>1390023.886868281</v>
       </c>
       <c r="AU3" t="n">
-        <v>74.92704517704517</v>
+        <v>71.42961139546952</v>
       </c>
       <c r="AV3" t="n">
-        <v>23.83518518518519</v>
+        <v>24.01830421040948</v>
       </c>
       <c r="AW3" t="n">
-        <v>178.3777777777778</v>
+        <v>179.6750866092971</v>
       </c>
       <c r="AX3" t="n">
         <v>1</v>
       </c>
       <c r="AY3" t="n">
-        <v>67.86481481481482</v>
+        <v>69.37028410186305</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1868796.296296296</v>
+        <v>2680220.780681307</v>
       </c>
       <c r="BA3" t="n">
-        <v>73.24629629629629</v>
+        <v>75.16107547423336</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2RU5F8AC</t>
+          <t>KfMnPVA4</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>p4iHBcGk</t>
+          <t>GW9jvbG8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pdWqnF1e</t>
+          <t>llkWcC07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45507.625</v>
+        <v>45513.79166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">lamolina n 
+          <t xml:space="preserve">herrera d 
   arg </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio jose amalfitani
-  buenos aires </t>
+          <t xml:space="preserve">estadio julio cesar villagra
+  cordoba </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>49540</v>
+        <v>34830</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UsCR8gFd</t>
+          <t>Amzaty2s</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gdfv0Zsh</t>
+          <t>lr2YMkTK</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1120,159 +1100,157 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ju1xJoJd</t>
+          <t>bkDdeAvA</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>zoYzAZW6</t>
+          <t>SAk2Byml</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>25</v>
+        <v>26.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>278</v>
+        <v>146</v>
       </c>
       <c r="U4" t="n">
-        <v>8950000</v>
+        <v>7100000</v>
       </c>
       <c r="V4" t="n">
-        <v>298</v>
-      </c>
-      <c r="W4" t="n">
-        <v>27</v>
-      </c>
-      <c r="X4" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>356</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>358</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>26.4</v>
+        <v>26.58226495726496</v>
       </c>
       <c r="AE4" t="n">
-        <v>177.8296296296296</v>
+        <v>180.3185897435897</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>1.026709401709402</v>
       </c>
       <c r="AG4" t="n">
-        <v>69.41481481481482</v>
+        <v>68.01388888888889</v>
       </c>
       <c r="AH4" t="n">
-        <v>1970370.37037037</v>
+        <v>1546223.290598291</v>
       </c>
       <c r="AI4" t="n">
-        <v>72.84444444444443</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
+        <v>71.55299145299145</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>27.41717171717171</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>180.2272727272727</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>69.56969696969696</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1606717.171717172</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>72.14646464646465</v>
+      </c>
       <c r="AP4" t="n">
-        <v>24.55614035087719</v>
+        <v>27.68888938737337</v>
       </c>
       <c r="AQ4" t="n">
-        <v>176.368671679198</v>
+        <v>179.0966841733146</v>
       </c>
       <c r="AR4" t="n">
-        <v>1</v>
+        <v>1.103605004834982</v>
       </c>
       <c r="AS4" t="n">
-        <v>68.85664160401002</v>
+        <v>67.94754086493218</v>
       </c>
       <c r="AT4" t="n">
-        <v>2859711.779448621</v>
+        <v>1461101.554814369</v>
       </c>
       <c r="AU4" t="n">
-        <v>74.94135338345865</v>
+        <v>71.53641692975216</v>
       </c>
       <c r="AV4" t="n">
-        <v>23.81328320802005</v>
+        <v>24.21385281385281</v>
       </c>
       <c r="AW4" t="n">
-        <v>180.8934837092732</v>
+        <v>177.5220238095238</v>
       </c>
       <c r="AX4" t="n">
         <v>1</v>
       </c>
       <c r="AY4" t="n">
-        <v>66.80075187969925</v>
+        <v>67.47012987012988</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1657644.110275689</v>
+        <v>1615647.772366523</v>
       </c>
       <c r="BA4" t="n">
-        <v>72.95112781954887</v>
+        <v>73.86016414141413</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>Czp8uYzj</t>
+          <t>YXLYMqz6</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>MkIVfIHA</t>
+          <t>KAydqpwC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vq1qlyXr</t>
+          <t>hMeNaYVf</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45507.71875</v>
+        <v>45513.875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">herrera d 
+          <t xml:space="preserve">arasa n 
   arg </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio mario alberto kempes
-  cordoba </t>
+          <t xml:space="preserve">estadio juan domingo peron
+  avellaneda </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>57000</v>
+        <v>61000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>bkDdeAvA</t>
+          <t>OhapHPm9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8G45bXRA</t>
+          <t>jiDN9Zaj</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1299,157 +1277,167 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Amzaty2s</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Amzaty2s</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+          <t>UVatI5Y2</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>178</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>74</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>74</v>
+      </c>
       <c r="W5" t="n">
-        <v>33</v>
+        <v>22.4</v>
       </c>
       <c r="X5" t="n">
-        <v>175</v>
+        <v>178.2</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>67</v>
+        <v>324</v>
       </c>
       <c r="AB5" t="n">
-        <v>500000</v>
+        <v>7200000</v>
       </c>
       <c r="AC5" t="n">
-        <v>67</v>
+        <v>367</v>
       </c>
       <c r="AD5" t="n">
-        <v>25.94006734006734</v>
+        <v>27.4375</v>
       </c>
       <c r="AE5" t="n">
-        <v>180.7986531986532</v>
+        <v>178.21875</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>1.09375</v>
       </c>
       <c r="AG5" t="n">
-        <v>70.18484848484849</v>
+        <v>72.625</v>
       </c>
       <c r="AH5" t="n">
-        <v>2561978.114478115</v>
+        <v>3141406.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>74.03602693602693</v>
+        <v>74.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23.71296296296296</v>
+        <v>26.072668997669</v>
       </c>
       <c r="AK5" t="n">
-        <v>177.6851851851852</v>
+        <v>177.0419774669775</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>67.23148148148148</v>
+        <v>67.99459984459985</v>
       </c>
       <c r="AN5" t="n">
-        <v>1948495.37037037</v>
+        <v>1522596.639471639</v>
       </c>
       <c r="AO5" t="n">
-        <v>72.01388888888889</v>
+        <v>72.23741258741258</v>
       </c>
       <c r="AP5" t="n">
-        <v>24.01957671957672</v>
+        <v>25.34139584484853</v>
       </c>
       <c r="AQ5" t="n">
-        <v>180.2746031746032</v>
+        <v>177.1860367112285</v>
       </c>
       <c r="AR5" t="n">
-        <v>1</v>
+        <v>1.036987046769656</v>
       </c>
       <c r="AS5" t="n">
-        <v>69.06243386243386</v>
+        <v>71.34996705482639</v>
       </c>
       <c r="AT5" t="n">
-        <v>2377447.08994709</v>
+        <v>2872882.68707706</v>
       </c>
       <c r="AU5" t="n">
-        <v>74.57671957671958</v>
+        <v>74.95387152631397</v>
       </c>
       <c r="AV5" t="n">
-        <v>24.55894638557177</v>
+        <v>25.04127277404869</v>
       </c>
       <c r="AW5" t="n">
-        <v>175.4282274313234</v>
+        <v>177.3488600437095</v>
       </c>
       <c r="AX5" t="n">
         <v>1</v>
       </c>
       <c r="AY5" t="n">
-        <v>66.36448965551132</v>
+        <v>66.69506456382712</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1352453.437515357</v>
+        <v>1325981.717093757</v>
       </c>
       <c r="BA5" t="n">
-        <v>70.7749766573296</v>
+        <v>70.85964003295108</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>W8lomLn5</t>
+          <t>8WPFLu92</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>KfMnPVA4</t>
+          <t>UL3R30aD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>U9B9fwfF</t>
+          <t>trGn6zgR</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45507.80208333334</v>
+        <v>45514.60416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">mastrangelo h 
+          <t xml:space="preserve">rey hilfer l 
   arg </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio libertadores de america
-  avellaneda </t>
+          <t xml:space="preserve">estadio pedro bidegain
+  buenos aires </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>48069</v>
+        <v>47964</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UVatI5Y2</t>
+          <t>ju1xJoJd</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ju1xJoJd</t>
+          <t>KpqpxWko</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1476,171 +1464,167 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>OhapHPm9</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
           <t>xd3lGq3F</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>23</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="Q6" t="n">
-        <v>169</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>70</v>
+        <v>208</v>
       </c>
       <c r="U6" t="n">
-        <v>3200000</v>
+        <v>8800000</v>
       </c>
       <c r="V6" t="n">
-        <v>77</v>
+        <v>229</v>
       </c>
       <c r="W6" t="n">
-        <v>27.66666666666667</v>
+        <v>24</v>
       </c>
       <c r="X6" t="n">
-        <v>182.6666666666667</v>
+        <v>181</v>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>208</v>
+        <v>62</v>
       </c>
       <c r="AB6" t="n">
-        <v>8800000</v>
+        <v>625000</v>
       </c>
       <c r="AC6" t="n">
-        <v>229</v>
+        <v>68</v>
       </c>
       <c r="AD6" t="n">
-        <v>26.96666666666667</v>
+        <v>25.022113997114</v>
       </c>
       <c r="AE6" t="n">
-        <v>181.1333333333333</v>
+        <v>178.3125721500722</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.033333333333333</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>70.06666666666666</v>
+        <v>69.96075036075037</v>
       </c>
       <c r="AH6" t="n">
-        <v>2049166.666666667</v>
+        <v>2934225.108225108</v>
       </c>
       <c r="AI6" t="n">
-        <v>74</v>
+        <v>74.82380952380952</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25.77777777777778</v>
+        <v>23.82927350427351</v>
       </c>
       <c r="AK6" t="n">
-        <v>176.8888888888889</v>
+        <v>178.959188034188</v>
       </c>
       <c r="AL6" t="n">
         <v>1</v>
       </c>
       <c r="AM6" t="n">
-        <v>70</v>
+        <v>67.41944444444445</v>
       </c>
       <c r="AN6" t="n">
-        <v>2877777.777777778</v>
+        <v>1955170.94017094</v>
       </c>
       <c r="AO6" t="n">
-        <v>74.33333333333333</v>
+        <v>72.7034188034188</v>
       </c>
       <c r="AP6" t="n">
-        <v>24.78042328042328</v>
+        <v>26.70331117374024</v>
       </c>
       <c r="AQ6" t="n">
-        <v>177.6772486772487</v>
+        <v>175.2266725669026</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.063492063492063</v>
+        <v>1</v>
       </c>
       <c r="AS6" t="n">
-        <v>68.93650793650794</v>
+        <v>69.29622131800737</v>
       </c>
       <c r="AT6" t="n">
-        <v>2144907.407407408</v>
+        <v>2053284.891461196</v>
       </c>
       <c r="AU6" t="n">
-        <v>75.06349206349206</v>
+        <v>73.44939503788017</v>
       </c>
       <c r="AV6" t="n">
-        <v>26.62996031746032</v>
+        <v>23.92897992100779</v>
       </c>
       <c r="AW6" t="n">
-        <v>175.7073412698413</v>
+        <v>178.4318978579041</v>
       </c>
       <c r="AX6" t="n">
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>69.14781746031746</v>
+        <v>66.11688120531001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1755009.920634921</v>
+        <v>1544781.615121205</v>
       </c>
       <c r="BA6" t="n">
-        <v>73.01587301587301</v>
+        <v>70.84458676858058</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
+          <t>xvR2CVDc</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
           <t>SdHeJ5BT</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>hhp5qLl8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KvUIXFn2</t>
+          <t>badJ0EGl</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45507.85416666666</v>
+        <v>45514.6875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">tello f 
+          <t xml:space="preserve">ramirez n 
   arg </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio tomas adolfo duco
-  buenos aires </t>
+          <t xml:space="preserve">estadio gigante de arroyito
+  rosario </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>48314</v>
+        <v>46955</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>xd3lGq3F</t>
+          <t>4QmJ2LNc</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>OhapHPm9</t>
+          <t>6gMiRHVj</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1667,26 +1651,40 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ju1xJoJd</t>
+          <t>6gMiRHVj</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>UVatI5Y2</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+          <t>4QmJ2LNc</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>182.75</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>281</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7400000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>293</v>
+      </c>
       <c r="W7" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="X7" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Y7" t="n">
         <v>1</v>
@@ -1695,117 +1693,129 @@
         <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="AB7" t="n">
-        <v>2900000</v>
+        <v>575000</v>
       </c>
       <c r="AC7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD7" t="n">
-        <v>27.55925925925926</v>
+        <v>26.14398148148148</v>
       </c>
       <c r="AE7" t="n">
-        <v>180.3407407407408</v>
+        <v>178.0199074074074</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>1.016666666666667</v>
       </c>
       <c r="AG7" t="n">
-        <v>68.67777777777779</v>
+        <v>70.11412037037037</v>
       </c>
       <c r="AH7" t="n">
-        <v>1606111.111111111</v>
+        <v>2591701.388888889</v>
       </c>
       <c r="AI7" t="n">
-        <v>71.47037037037036</v>
-      </c>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
+        <v>74.26620370370371</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>26.28484848484848</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>177.3920875420876</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.073063973063973</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>69.03998316498316</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>2031929.713804714</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>72.79688552188551</v>
+      </c>
       <c r="AP7" t="n">
-        <v>25.53899240855762</v>
+        <v>24.27081663275995</v>
       </c>
       <c r="AQ7" t="n">
-        <v>177.7159247757074</v>
+        <v>176.9505113472963</v>
       </c>
       <c r="AR7" t="n">
         <v>1</v>
       </c>
       <c r="AS7" t="n">
-        <v>68.08928571428571</v>
+        <v>68.84510216966754</v>
       </c>
       <c r="AT7" t="n">
-        <v>1889212.387853692</v>
+        <v>2491642.101091732</v>
       </c>
       <c r="AU7" t="n">
-        <v>72.59411663216009</v>
+        <v>74.52806381229578</v>
       </c>
       <c r="AV7" t="n">
-        <v>25.05550887021475</v>
+        <v>23.55459343288291</v>
       </c>
       <c r="AW7" t="n">
-        <v>176.7782913165266</v>
+        <v>175.503223311776</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.015873015873016</v>
+        <v>1.036753524253524</v>
       </c>
       <c r="AY7" t="n">
-        <v>70.93398692810457</v>
+        <v>65.96570030846345</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2554570.494864612</v>
+        <v>1588151.329664488</v>
       </c>
       <c r="BA7" t="n">
-        <v>75.0688608776844</v>
+        <v>72.81919666590719</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>8rrQkbdH</t>
+          <t>xYveDhra</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>xIZruiA3</t>
+          <t>IFbJwyX4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bPuAZyIk</t>
+          <t>2iHr7GwL</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45508.625</v>
+        <v>45514.78125</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ramirez n 
+          <t xml:space="preserve">tello f 
   arg </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio eva peron
-  junin </t>
+          <t xml:space="preserve">estadio juan bautista gargantini
+  mendoza </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KQ6kGfyc</t>
+          <t>Eg51aDC4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amzaty2s</t>
+          <t>hMrWAFH0</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1830,21 +1840,17 @@
           <t>liga profesional</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>80MMdBdN</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>bkDdeAvA</t>
+          <t>EVqSBe2f</t>
         </is>
       </c>
       <c r="P8" t="n">
         <v>27</v>
       </c>
       <c r="Q8" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1853,7 +1859,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U8" t="n">
         <v>975000</v>
@@ -1861,128 +1867,130 @@
       <c r="V8" t="n">
         <v>67</v>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="n">
-        <v>24.875</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>176.625</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>66</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1281250</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>71.625</v>
-      </c>
+      <c r="W8" t="n">
+        <v>26</v>
+      </c>
+      <c r="X8" t="n">
+        <v>178</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>72</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>73</v>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="n">
-        <v>26.46759259259259</v>
+        <v>28.49722222222222</v>
       </c>
       <c r="AK8" t="n">
-        <v>180.1296296296296</v>
+        <v>181.4180555555556</v>
       </c>
       <c r="AL8" t="n">
-        <v>1</v>
+        <v>1.576157407407408</v>
       </c>
       <c r="AM8" t="n">
-        <v>67.56018518518518</v>
+        <v>74.17986111111112</v>
       </c>
       <c r="AN8" t="n">
-        <v>1410069.444444445</v>
+        <v>4472569.444444445</v>
       </c>
       <c r="AO8" t="n">
-        <v>71</v>
+        <v>77.18055555555556</v>
       </c>
       <c r="AP8" t="n">
-        <v>25.51520467836258</v>
+        <v>25.85294705294705</v>
       </c>
       <c r="AQ8" t="n">
-        <v>180.9754385964912</v>
+        <v>176.6448717948718</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.137816764132554</v>
+        <v>1</v>
       </c>
       <c r="AS8" t="n">
-        <v>65.74307992202728</v>
+        <v>66.65149017649017</v>
       </c>
       <c r="AT8" t="n">
-        <v>1005908.382066277</v>
+        <v>1182765.151515151</v>
       </c>
       <c r="AU8" t="n">
-        <v>70.43976608187134</v>
+        <v>71.13910256410257</v>
       </c>
       <c r="AV8" t="n">
-        <v>27.82373737373737</v>
+        <v>25.63644281048616</v>
       </c>
       <c r="AW8" t="n">
-        <v>180.0025252525253</v>
+        <v>177.8747491961083</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.174242424242424</v>
+        <v>1.144027330083058</v>
       </c>
       <c r="AY8" t="n">
-        <v>67.6969696969697</v>
+        <v>71.0524563522706</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1352121.212121212</v>
+        <v>3507808.36353762</v>
       </c>
       <c r="BA8" t="n">
-        <v>71.37373737373737</v>
+        <v>76.71730043148</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>2Z11gzUL</t>
+          <t>fVnsh4kN</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>INpzsZkg</t>
+          <t>tdzQkXt9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tlVEYeXe</t>
+          <t>WCfRbho1</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45508.625</v>
+        <v>45514.85416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">echavarria p 
+          <t xml:space="preserve">echenique f 
   arg </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio 15 de abril
-  santa fe </t>
+          <t xml:space="preserve">estadio monumental
+  buenos aires </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>27358</v>
+        <v>84567</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>lr2YMkTK</t>
+          <t>EVqSBe2f</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EVqSBe2f</t>
+          <t>xd3lGq3F</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2009,113 +2017,113 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>SAk2Byml</t>
+          <t>hMrWAFH0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>hMrWAFH0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="n">
-        <v>30</v>
-      </c>
-      <c r="X9" t="n">
-        <v>172</v>
-      </c>
-      <c r="Y9" t="n">
+          <t>ju1xJoJd</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="Z9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>75</v>
-      </c>
+      <c r="T9" t="n">
+        <v>148</v>
+      </c>
+      <c r="U9" t="n">
+        <v>8600000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>148</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
-        <v>27.29629629629629</v>
+        <v>27.47850168350168</v>
       </c>
       <c r="AE9" t="n">
-        <v>180.5185185185185</v>
+        <v>178.9690067340067</v>
       </c>
       <c r="AF9" t="n">
-        <v>1</v>
+        <v>1.05526936026936</v>
       </c>
       <c r="AG9" t="n">
-        <v>69.07407407407406</v>
+        <v>73.5627946127946</v>
       </c>
       <c r="AH9" t="n">
-        <v>1477777.777777778</v>
+        <v>5348928.451178451</v>
       </c>
       <c r="AI9" t="n">
-        <v>71.85185185185185</v>
+        <v>76.66621212121213</v>
       </c>
       <c r="AJ9" t="n">
-        <v>27.58240740740741</v>
+        <v>27.17008547008547</v>
       </c>
       <c r="AK9" t="n">
-        <v>178.7416666666667</v>
+        <v>180.6324786324786</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.075</v>
+        <v>1</v>
       </c>
       <c r="AM9" t="n">
-        <v>72.77592592592593</v>
+        <v>68.75299145299147</v>
       </c>
       <c r="AN9" t="n">
-        <v>5138157.407407408</v>
+        <v>1670277.777777778</v>
       </c>
       <c r="AO9" t="n">
-        <v>75.55833333333334</v>
+        <v>71.57948717948717</v>
       </c>
       <c r="AP9" t="n">
-        <v>24.26136363636364</v>
+        <v>25.49397097266662</v>
       </c>
       <c r="AQ9" t="n">
-        <v>176.4305555555556</v>
+        <v>177.9886148440931</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>1.15591756070017</v>
       </c>
       <c r="AS9" t="n">
-        <v>67.75631313131315</v>
+        <v>72.22264004433571</v>
       </c>
       <c r="AT9" t="n">
-        <v>1705239.898989899</v>
+        <v>5116384.142041534</v>
       </c>
       <c r="AU9" t="n">
-        <v>73.99621212121212</v>
+        <v>76.59392925110318</v>
       </c>
       <c r="AV9" t="n">
-        <v>27.28787878787879</v>
+        <v>25.8302269989796</v>
       </c>
       <c r="AW9" t="n">
-        <v>179.665404040404</v>
+        <v>177.5869840461681</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.21969696969697</v>
+        <v>1</v>
       </c>
       <c r="AY9" t="n">
-        <v>73.5239898989899</v>
+        <v>67.7595618849916</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4913914.141414142</v>
+        <v>1703670.600901803</v>
       </c>
       <c r="BA9" t="n">
-        <v>76.62626262626263</v>
+        <v>72.23819577871831</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
@@ -2124,42 +2132,42 @@
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>YXLYMqz6</t>
+          <t>r9zDZa4I</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>xzFHhHOR</t>
+          <t>vJVmoZG1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45508.72916666666</v>
+        <v>45515.625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">echenique f 
+          <t xml:space="preserve">espinoza f 
   arg </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio alberto j  armando
-  buenos aires </t>
+          <t xml:space="preserve">estadio unico madre de ciudades
+  santiago del estero </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>57200</v>
+        <v>42000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>hMrWAFH0</t>
+          <t>0dHZReql</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>hW08cP6J</t>
+          <t>Gdfv0Zsh</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2184,21 +2192,17 @@
           <t>liga profesional</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>EVqSBe2f</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>xd3lGq3F</t>
+          <t>zoYzAZW6</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q10" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -2207,150 +2211,150 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="U10" t="n">
-        <v>2500000</v>
+        <v>650000</v>
       </c>
       <c r="V10" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="W10" t="n">
-        <v>22</v>
+        <v>26.5</v>
       </c>
       <c r="X10" t="n">
-        <v>172</v>
+        <v>179.5</v>
       </c>
       <c r="Y10" t="n">
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000000</v>
+        <v>6700000</v>
       </c>
       <c r="AC10" t="n">
-        <v>72</v>
+        <v>147</v>
       </c>
       <c r="AD10" t="n">
-        <v>30.375</v>
+        <v>24.91576879910214</v>
       </c>
       <c r="AE10" t="n">
-        <v>181.875</v>
+        <v>178.957379349046</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.875</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
-        <v>74.875</v>
+        <v>66.09988776655445</v>
       </c>
       <c r="AH10" t="n">
-        <v>3962500</v>
+        <v>1335912.317620651</v>
       </c>
       <c r="AI10" t="n">
-        <v>76.625</v>
+        <v>71.41837822671157</v>
       </c>
       <c r="AJ10" t="n">
-        <v>24.61111111111111</v>
+        <v>25.79691358024691</v>
       </c>
       <c r="AK10" t="n">
-        <v>178</v>
+        <v>181.2388888888889</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
       </c>
       <c r="AM10" t="n">
-        <v>66.97222222222223</v>
+        <v>68.22376543209877</v>
       </c>
       <c r="AN10" t="n">
-        <v>1496527.777777778</v>
+        <v>1640401.234567901</v>
       </c>
       <c r="AO10" t="n">
-        <v>71.94444444444444</v>
+        <v>71.94876543209877</v>
       </c>
       <c r="AP10" t="n">
-        <v>26.55436720142602</v>
+        <v>23.71442388021335</v>
       </c>
       <c r="AQ10" t="n">
-        <v>178.6257957728546</v>
+        <v>177.7444653299917</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.169467787114846</v>
+        <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>70.53323147440796</v>
+        <v>65.81477732793522</v>
       </c>
       <c r="AT10" t="n">
-        <v>2745409.982174688</v>
+        <v>1438686.013912988</v>
       </c>
       <c r="AU10" t="n">
-        <v>75.64514896867838</v>
+        <v>72.42485862091125</v>
       </c>
       <c r="AV10" t="n">
-        <v>24.15711462450593</v>
+        <v>24.27035023456076</v>
       </c>
       <c r="AW10" t="n">
-        <v>177.3883399209486</v>
+        <v>180.7452921548563</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>65.83300395256917</v>
+        <v>66.15962467079638</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1382633.399209486</v>
+        <v>1573933.848762177</v>
       </c>
       <c r="BA10" t="n">
-        <v>71.33300395256917</v>
+        <v>72.63152549258051</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>KfMnPVA4</t>
+          <t>YgyxEvnR</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>fVnsh4kN</t>
+          <t>6ueHTT9o</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rDFDgc9L</t>
+          <t>fRDz9x98</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45508.83333333334</v>
+        <v>45515.625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">arasa n 
+          <t xml:space="preserve">balino j 
   arg </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio monumental jose fierro
-  tucuman </t>
+          <t xml:space="preserve">estadio presidente peron
+  cordoba </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>35200</v>
+        <v>26000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KpqpxWko</t>
+          <t>8G45bXRA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eg51aDC4</t>
+          <t>80MMdBdN</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2375,13 +2379,17 @@
           <t>liga profesional</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Amzaty2s</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="Q11" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -2390,114 +2398,126 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="U11" t="n">
-        <v>625000</v>
+        <v>500000</v>
       </c>
       <c r="V11" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="W11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X11" t="n">
-        <v>163</v>
+        <v>177.8</v>
       </c>
       <c r="Y11" t="n">
         <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>67</v>
+        <v>336</v>
       </c>
       <c r="AB11" t="n">
-        <v>975000</v>
+        <v>5300000</v>
       </c>
       <c r="AC11" t="n">
-        <v>67</v>
+        <v>347</v>
       </c>
       <c r="AD11" t="n">
-        <v>23.95833333333333</v>
+        <v>25.02083333333333</v>
       </c>
       <c r="AE11" t="n">
-        <v>179.2083333333333</v>
+        <v>177.1037037037037</v>
       </c>
       <c r="AF11" t="n">
         <v>1</v>
       </c>
       <c r="AG11" t="n">
-        <v>67.08333333333333</v>
+        <v>67.95694444444445</v>
       </c>
       <c r="AH11" t="n">
-        <v>1952083.333333333</v>
+        <v>1971313.657407407</v>
       </c>
       <c r="AI11" t="n">
-        <v>71.91666666666667</v>
-      </c>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
+        <v>71.63958333333333</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>25.39720279720279</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>180.813986013986</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>66.95034965034966</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1291153.846153846</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>70.41398601398602</v>
+      </c>
       <c r="AP11" t="n">
-        <v>24.31851851851852</v>
+        <v>25.54111094730289</v>
       </c>
       <c r="AQ11" t="n">
-        <v>179.6888888888889</v>
+        <v>176.1719176506328</v>
       </c>
       <c r="AR11" t="n">
         <v>1</v>
       </c>
       <c r="AS11" t="n">
-        <v>66.34444444444445</v>
+        <v>66.29832930514044</v>
       </c>
       <c r="AT11" t="n">
-        <v>1496296.296296296</v>
+        <v>1201854.588193598</v>
       </c>
       <c r="AU11" t="n">
-        <v>70.60000000000001</v>
+        <v>69.72888350183241</v>
       </c>
       <c r="AV11" t="n">
-        <v>23.14848484848484</v>
+        <v>23.99581735621782</v>
       </c>
       <c r="AW11" t="n">
-        <v>176.4333333333333</v>
+        <v>178.0567105189073</v>
       </c>
       <c r="AX11" t="n">
         <v>1</v>
       </c>
       <c r="AY11" t="n">
-        <v>65.87272727272726</v>
+        <v>66.04041325654597</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1303787.878787879</v>
+        <v>1415256.102434306</v>
       </c>
       <c r="BA11" t="n">
-        <v>73.2</v>
+        <v>71.63031830065012</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>tdzQkXt9</t>
+          <t>IPCvd5Pa</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>zTfUpJig</t>
+          <t>W8lomLn5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>U9kvubfS</t>
+          <t>hMZipgW7</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45508.83333333334</v>
+        <v>45515.72916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2507,21 +2527,21 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ciudad de lanus – nestor diaz perez
-  lanus </t>
+          <t xml:space="preserve">estadio florencio sola
+  buenos aires </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>47090</v>
+        <v>34902</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Y9yh1J7G</t>
+          <t>GIb40wNM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>nkwO1uw4</t>
+          <t>UsCR8gFd</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2548,157 +2568,171 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>GIb40wNM</t>
+          <t>Y9yh1J7G</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>80MMdBdN</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+          <t>ju1xJoJd</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>128</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2125000</v>
+      </c>
+      <c r="V12" t="n">
+        <v>142</v>
+      </c>
       <c r="W12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X12" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Y12" t="n">
         <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000000</v>
+        <v>2150000</v>
       </c>
       <c r="AC12" t="n">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="AD12" t="n">
-        <v>27.25462962962963</v>
+        <v>26.46666666666667</v>
       </c>
       <c r="AE12" t="n">
-        <v>178.6157407407407</v>
+        <v>179.1032828282828</v>
       </c>
       <c r="AF12" t="n">
         <v>1</v>
       </c>
       <c r="AG12" t="n">
-        <v>70.3425925925926</v>
+        <v>67.24520202020202</v>
       </c>
       <c r="AH12" t="n">
-        <v>2891898.148148148</v>
+        <v>1300042.929292929</v>
       </c>
       <c r="AI12" t="n">
-        <v>73.07407407407408</v>
+        <v>72.00580808080808</v>
       </c>
       <c r="AJ12" t="n">
-        <v>23.125</v>
+        <v>25.6937908496732</v>
       </c>
       <c r="AK12" t="n">
-        <v>178.75</v>
+        <v>178.0771241830065</v>
       </c>
       <c r="AL12" t="n">
         <v>1</v>
       </c>
       <c r="AM12" t="n">
-        <v>65.5625</v>
+        <v>69.87924836601306</v>
       </c>
       <c r="AN12" t="n">
-        <v>1443750</v>
+        <v>2244297.385620915</v>
       </c>
       <c r="AO12" t="n">
-        <v>71.9375</v>
+        <v>74.05114379084968</v>
       </c>
       <c r="AP12" t="n">
-        <v>26.62222222222222</v>
+        <v>24.137723314697</v>
       </c>
       <c r="AQ12" t="n">
-        <v>178.3813725490196</v>
+        <v>178.9596965169333</v>
       </c>
       <c r="AR12" t="n">
         <v>1</v>
       </c>
       <c r="AS12" t="n">
-        <v>69.34542483660131</v>
+        <v>65.71495324850588</v>
       </c>
       <c r="AT12" t="n">
-        <v>2276813.725490196</v>
+        <v>1199703.766628109</v>
       </c>
       <c r="AU12" t="n">
-        <v>73.63496732026144</v>
+        <v>71.45817588843904</v>
       </c>
       <c r="AV12" t="n">
-        <v>23.63876319758673</v>
+        <v>24.61187512102418</v>
       </c>
       <c r="AW12" t="n">
-        <v>177.7096530920061</v>
+        <v>177.6340412359853</v>
       </c>
       <c r="AX12" t="n">
         <v>1</v>
       </c>
       <c r="AY12" t="n">
-        <v>65.7733785822021</v>
+        <v>68.68102257017756</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1296910.350678733</v>
+        <v>2250701.210952133</v>
       </c>
       <c r="BA12" t="n">
-        <v>70.90422322775264</v>
+        <v>74.12414361751686</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>IH9zbCEt</t>
+          <t>MkIVfIHA</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>YgyxEvnR</t>
+          <t>joU5U5WF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>jJjztvuM</t>
+          <t>nPhF1f1r</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45509.60416666666</v>
+        <v>45515.83333333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">rey hilfer l 
+          <t xml:space="preserve">zunino s 
   arg </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio guillermo laza
-  buenos aires </t>
+          <t xml:space="preserve">estadio jorge luis hirschi
+  la plata </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3000</v>
+        <v>32530</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2iZ4q0z6</t>
+          <t>p2SkCHXs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0dHZReql</t>
+          <t>UVatI5Y2</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2724,112 +2758,168 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>OhapHPm9</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>176</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>69</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="V13" t="n">
+        <v>72</v>
+      </c>
+      <c r="W13" t="n">
+        <v>19</v>
+      </c>
+      <c r="X13" t="n">
+        <v>174</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>28.47037037037037</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>177.2348148148148</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.124444444444445</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>71.82222222222222</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3015981.481481482</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>74.20148148148148</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>28.03057498057499</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>180.7992618492619</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.111519036519037</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>71.05260295260295</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2216594.794094794</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>73.97228049728049</v>
+      </c>
       <c r="AP13" t="n">
-        <v>29.88888888888889</v>
+        <v>27.08992079957553</v>
       </c>
       <c r="AQ13" t="n">
-        <v>178.7555555555556</v>
+        <v>178.3813470204135</v>
       </c>
       <c r="AR13" t="n">
-        <v>1</v>
+        <v>1.172303378633302</v>
       </c>
       <c r="AS13" t="n">
-        <v>66.67777777777778</v>
+        <v>68.89509703851138</v>
       </c>
       <c r="AT13" t="n">
-        <v>715000</v>
+        <v>1722495.507476326</v>
       </c>
       <c r="AU13" t="n">
-        <v>67.05555555555556</v>
+        <v>72.77920857914465</v>
       </c>
       <c r="AV13" t="n">
-        <v>23.02380952380952</v>
+        <v>24.96782717031586</v>
       </c>
       <c r="AW13" t="n">
-        <v>177.6765873015873</v>
+        <v>177.3944159912486</v>
       </c>
       <c r="AX13" t="n">
-        <v>1</v>
+        <v>1.055736495781745</v>
       </c>
       <c r="AY13" t="n">
-        <v>65.56150793650794</v>
+        <v>69.30535693567369</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1474255.952380952</v>
+        <v>2336616.569704805</v>
       </c>
       <c r="BA13" t="n">
-        <v>73.2063492063492</v>
+        <v>75.0125376383295</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>nozaSkhA</t>
+          <t>hhp5qLl8</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>joU5U5WF</t>
+          <t>xvR2CVDc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8fN0daP2</t>
+          <t>trxILFhE</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45509.70833333334</v>
+        <v>45516.79166666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">zunino s 
+          <t xml:space="preserve">gariano a 
   arg </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio juan carmelo zerillo
-  la plata </t>
+          <t xml:space="preserve">estadio jose dellagiovanna
+  buenos aires </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>21500</v>
+        <v>26282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>jiDN9Zaj</t>
+          <t>nkwO1uw4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4QmJ2LNc</t>
+          <t>tUAxIm6l</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2854,12 +2944,12 @@
           <t>liga profesional</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>6gMiRHVj</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>80MMdBdN</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -2875,130 +2965,130 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
-        <v>26.65656565656566</v>
+        <v>23.46111111111111</v>
       </c>
       <c r="AE14" t="n">
-        <v>177.1346801346801</v>
+        <v>179.1708333333333</v>
       </c>
       <c r="AF14" t="n">
         <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>67.54882154882155</v>
+        <v>65.76944444444445</v>
       </c>
       <c r="AH14" t="n">
-        <v>1335858.585858586</v>
+        <v>1444236.111111111</v>
       </c>
       <c r="AI14" t="n">
-        <v>71.28619528619528</v>
+        <v>71.8875</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26.26851851851852</v>
+        <v>25.72777777777778</v>
       </c>
       <c r="AK14" t="n">
-        <v>177.5462962962963</v>
+        <v>179.5166666666667</v>
       </c>
       <c r="AL14" t="n">
         <v>1</v>
       </c>
       <c r="AM14" t="n">
-        <v>69.98611111111113</v>
+        <v>71.37222222222222</v>
       </c>
       <c r="AN14" t="n">
-        <v>2326620.37037037</v>
+        <v>3096388.888888889</v>
       </c>
       <c r="AO14" t="n">
-        <v>74.02777777777779</v>
+        <v>75.27777777777777</v>
       </c>
       <c r="AP14" t="n">
-        <v>24.44814814814815</v>
+        <v>23.65501720417674</v>
       </c>
       <c r="AQ14" t="n">
-        <v>178.1777777777778</v>
+        <v>177.8936302193529</v>
       </c>
       <c r="AR14" t="n">
         <v>1</v>
       </c>
       <c r="AS14" t="n">
-        <v>66.52222222222223</v>
+        <v>65.3872456117341</v>
       </c>
       <c r="AT14" t="n">
-        <v>1339074.074074074</v>
+        <v>1253173.684796558</v>
       </c>
       <c r="AU14" t="n">
-        <v>70.76666666666667</v>
+        <v>70.90064740368364</v>
       </c>
       <c r="AV14" t="n">
-        <v>24.57502546473135</v>
+        <v>22.86609369388781</v>
       </c>
       <c r="AW14" t="n">
-        <v>176.5509994907054</v>
+        <v>180.3475892408245</v>
       </c>
       <c r="AX14" t="n">
         <v>1</v>
       </c>
       <c r="AY14" t="n">
-        <v>69.31285332314744</v>
+        <v>68.23489693313222</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2911391.170104405</v>
+        <v>2323057.952668247</v>
       </c>
       <c r="BA14" t="n">
-        <v>74.52869238604532</v>
+        <v>74.2603086619263</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>IFbJwyX4</t>
+          <t>p4iHBcGk</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>8rrQkbdH</t>
+          <t>IH9zbCEt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>65Xumenk</t>
+          <t>Y9EiyTMr</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45509.83333333334</v>
+        <v>45518.79166666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">penel a 
+          <t xml:space="preserve">tello f 
   arg </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio ciudad de vicente lopez
-  buenos aires </t>
+          <t xml:space="preserve">estadio libertadores de america
+  avellaneda </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>28530</v>
+        <v>48069</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>80MMdBdN</t>
+          <t>QuxS0ahA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>GIb40wNM</t>
+          <t>xd3lGq3F</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>2024</v>
@@ -3010,13 +3100,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>liga profesional</t>
+          <t>copa argentina</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Y9yh1J7G</t>
+          <t>ju1xJoJd</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -3034,130 +3124,130 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="n">
-        <v>25.55151515151515</v>
+        <v>23.32569444444444</v>
       </c>
       <c r="AE15" t="n">
-        <v>180.7909090909091</v>
+        <v>178.8041666666666</v>
       </c>
       <c r="AF15" t="n">
         <v>1</v>
       </c>
       <c r="AG15" t="n">
-        <v>67.41818181818182</v>
+        <v>69.36250000000001</v>
       </c>
       <c r="AH15" t="n">
-        <v>1389621.212121212</v>
+        <v>2920937.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>70.7060606060606</v>
+        <v>75.48472222222222</v>
       </c>
       <c r="AJ15" t="n">
-        <v>25.03472222222222</v>
+        <v>27.17008547008547</v>
       </c>
       <c r="AK15" t="n">
-        <v>178.9236111111111</v>
+        <v>180.6324786324786</v>
       </c>
       <c r="AL15" t="n">
         <v>1</v>
       </c>
       <c r="AM15" t="n">
-        <v>66.40972222222223</v>
+        <v>68.75299145299147</v>
       </c>
       <c r="AN15" t="n">
-        <v>1283506.944444444</v>
+        <v>1670277.777777778</v>
       </c>
       <c r="AO15" t="n">
-        <v>72.34027777777777</v>
+        <v>71.57948717948717</v>
       </c>
       <c r="AP15" t="n">
-        <v>24.08575757575757</v>
+        <v>23.67741934144073</v>
       </c>
       <c r="AQ15" t="n">
-        <v>179.0893939393939</v>
+        <v>177.2816028708134</v>
       </c>
       <c r="AR15" t="n">
         <v>1</v>
       </c>
       <c r="AS15" t="n">
-        <v>67.35424242424243</v>
+        <v>68.12453141613503</v>
       </c>
       <c r="AT15" t="n">
-        <v>1740053.03030303</v>
+        <v>1965815.149853801</v>
       </c>
       <c r="AU15" t="n">
-        <v>72.19787878787879</v>
+        <v>73.59304259702286</v>
       </c>
       <c r="AV15" t="n">
-        <v>24.24074074074074</v>
+        <v>25.8302269989796</v>
       </c>
       <c r="AW15" t="n">
-        <v>176.8468915343915</v>
+        <v>177.5869840461681</v>
       </c>
       <c r="AX15" t="n">
         <v>1</v>
       </c>
       <c r="AY15" t="n">
-        <v>66.78505291005291</v>
+        <v>67.7595618849916</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1370634.920634921</v>
+        <v>1703670.600901803</v>
       </c>
       <c r="BA15" t="n">
-        <v>71.98511904761905</v>
+        <v>72.23819577871831</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>6ueHTT9o</t>
+          <t>IH9zbCEt</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>W8lomLn5</t>
+          <t>r9zDZa4I</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SvlzcWFD</t>
+          <t>fgvPVMI8</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45512.625</v>
+        <v>45519.70833333334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">arasa n 
+          <t xml:space="preserve">penel a 
   arg </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">estadio diego armando maradona
-  buenos aires </t>
+          <t xml:space="preserve">estadio centenario ciudad de quilmes
+  quilmes </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>26000</v>
+        <v>30200</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>QuxS0ahA</t>
+          <t>ABogdBtb</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>KQ6kGfyc</t>
+          <t>GIb40wNM</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>2024</v>
@@ -3169,13 +3259,13 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>liga profesional</t>
+          <t>copa argentina</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>80MMdBdN</t>
+          <t>Y9yh1J7G</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -3192,249 +3282,62 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>178.925925925926</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>69.1111111111111</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2338888.888888889</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>74.81481481481482</v>
-      </c>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="n">
-        <v>24.875</v>
+        <v>26.46666666666667</v>
       </c>
       <c r="AK16" t="n">
-        <v>176.625</v>
+        <v>179.1032828282828</v>
       </c>
       <c r="AL16" t="n">
         <v>1</v>
       </c>
       <c r="AM16" t="n">
-        <v>66</v>
+        <v>67.24520202020202</v>
       </c>
       <c r="AN16" t="n">
-        <v>1281250</v>
+        <v>1300042.929292929</v>
       </c>
       <c r="AO16" t="n">
-        <v>71.625</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>23.83518518518519</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>178.3777777777778</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>67.86481481481482</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1868796.296296296</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>73.24629629629629</v>
-      </c>
+        <v>72.00580808080808</v>
+      </c>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
       <c r="AV16" t="n">
-        <v>25.51520467836258</v>
+        <v>24.137723314697</v>
       </c>
       <c r="AW16" t="n">
-        <v>180.9754385964912</v>
+        <v>178.9596965169333</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.137816764132554</v>
+        <v>1</v>
       </c>
       <c r="AY16" t="n">
-        <v>65.74307992202728</v>
+        <v>65.71495324850588</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1005908.382066277</v>
+        <v>1199703.766628109</v>
       </c>
       <c r="BA16" t="n">
-        <v>70.43976608187134</v>
+        <v>71.45817588843904</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>IH9zbCEt</t>
+          <t>xtEjMiPE</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>YXLYMqz6</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ngdGLTFj</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45510.88194444445</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">herrera d 
-  arg </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">estadio libertadores de america
-  avellaneda </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>48069</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ju1xJoJd</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>UsCR8gFd</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>6</v>
-      </c>
-      <c r="I17" t="n">
-        <v>64</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>argentina</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>copa argentina</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>xd3lGq3F</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>ju1xJoJd</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="n">
-        <v>25.77777777777778</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>176.8888888888889</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2877777.777777778</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>74.33333333333333</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>177.8296296296296</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>69.41481481481482</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1970370.37037037</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>72.84444444444443</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>26.62996031746032</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>175.7073412698413</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>69.14781746031746</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1755009.920634921</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>73.01587301587301</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>24.55614035087719</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>176.368671679198</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>68.85664160401002</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>2859711.779448621</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>74.94135338345865</v>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>xvR2CVDc</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>joU5U5WF</t>
+          <t>W8lomLn5</t>
         </is>
       </c>
     </row>
